--- a/mes-plugins/mes-plugins-master-orders/src/main/resources/masterOrders/public/resources/masterOrderImportSchema_cn.xlsx
+++ b/mes-plugins/mes-plugins-master-orders/src/main/resources/masterOrders/public/resources/masterOrderImportSchema_cn.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/krna/Projects/mes/mes-plugins/mes-plugins-master-orders/src/main/resources/masterOrders/public/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liuho\Desktop\Import templates - 副本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBC0E1D4-DEB9-904D-81A6-39898556C0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A4A53C-61D6-40FC-903D-4A0BD79C21E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="23260" windowHeight="12460" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales orders position" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -56,7 +55,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -81,7 +79,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -90,7 +87,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -110,7 +106,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t>qcadoo</t>
         </r>
@@ -134,7 +129,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -143,7 +137,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -168,7 +161,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -177,7 +169,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -197,7 +188,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t xml:space="preserve">. </t>
         </r>
@@ -221,7 +211,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -230,7 +219,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -250,7 +238,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t xml:space="preserve">. </t>
         </r>
@@ -274,7 +261,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -283,7 +269,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -303,7 +288,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t xml:space="preserve">. </t>
         </r>
@@ -322,7 +306,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t>.</t>
         </r>
@@ -336,7 +319,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -345,7 +327,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -365,7 +346,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t xml:space="preserve">. </t>
         </r>
@@ -384,7 +364,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t xml:space="preserve"> </t>
         </r>
@@ -403,7 +382,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t>: YYYY-MM-DD HH:MM:SS</t>
         </r>
@@ -417,7 +395,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -426,7 +403,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -446,7 +422,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t xml:space="preserve">. </t>
         </r>
@@ -465,7 +440,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t xml:space="preserve"> </t>
         </r>
@@ -484,7 +458,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t>: YYYY-MM-DD HH:MM:SS</t>
         </r>
@@ -498,7 +471,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -507,7 +479,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -527,7 +498,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t xml:space="preserve">. 
 </t>
@@ -547,7 +517,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t>: YYYY-MM-DD HH:MM:SS</t>
         </r>
@@ -561,7 +530,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -570,7 +538,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -590,7 +557,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t xml:space="preserve">. </t>
         </r>
@@ -609,7 +575,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -629,7 +594,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t>: YYYY-MM-DD HH:MM:SS</t>
         </r>
@@ -643,7 +607,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -652,7 +615,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -672,7 +634,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t>.</t>
         </r>
@@ -686,7 +647,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -695,7 +655,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -715,7 +674,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t xml:space="preserve">. </t>
         </r>
@@ -734,7 +692,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t>qcadoo</t>
         </r>
@@ -755,7 +712,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t xml:space="preserve"> </t>
         </r>
@@ -769,7 +725,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -778,7 +733,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -803,7 +757,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -812,7 +765,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -832,7 +784,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
           </rPr>
           <t>:</t>
         </r>
@@ -853,7 +804,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>编号</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -910,12 +861,6 @@
     <t>接单日期</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
-  <si>
-    <t>Delivery date of position</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
 </sst>
 </file>
 
@@ -949,13 +894,11 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1023,21 +966,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <charset val="238"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <charset val="238"/>
-      </font>
-    </dxf>
+  <dxfs count="17">
     <dxf>
       <font>
         <b val="0"/>
@@ -1172,7 +1103,7 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Styl tabeli 1" pivot="0" count="1" xr9:uid="{7F7E74EB-FAA7-4CC6-8588-50EB3079B849}">
-      <tableStyleElement type="wholeTable" dxfId="18"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1829,34 +1760,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{509C9033-BB95-4FBE-92A0-4CB515E0BEFD}" name="masterOrderImportSchema_en" displayName="masterOrderImportSchema_en" ref="A1:P2" insertRow="1" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
-  <autoFilter ref="A1:P2" xr:uid="{509C9033-BB95-4FBE-92A0-4CB515E0BEFD}"/>
-  <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{23FABA08-3273-4AB7-9597-4F5A70C4A802}" name="编号" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{333E4883-B023-4214-B42A-2955249499F1}" name="产品编号" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{C2C5E57D-6FF8-4AC2-9D39-0F486D2B0635}" name="数量" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{38BDA567-1F2F-4129-9971-CACDFC7230DF}" name="销售订单名称" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{712BB09D-F8B5-4BA0-8C6B-67E1428AD39D}" name="描述" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{D782C7E9-A47A-4544-AB5D-4D3E4A34E11C}" name="客户" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{8F187897-00A6-4184-9F3D-C9E9D6FFAE1A}" name="开始日期" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{2AEE7656-FC19-4A25-8B27-7F10864D6B66}" name="结束日期" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{0788B078-0DB2-449F-8885-09A8766A36F3}" name="截止日期" dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{200873D5-3A9E-4F92-9648-637A95B6FF84}" name="接单日期" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{07928C99-1DDA-4CFC-AAC0-A58D0AC5D66A}" name="状态描述" dataDxfId="5"/>
-    <tableColumn id="12" xr3:uid="{AA8ABAE0-75A6-49F4-8A32-AA80FCA4EBD7}" name="工艺" dataDxfId="4"/>
-    <tableColumn id="13" xr3:uid="{404241C0-BE8D-4E09-8909-BD1C6A0AB30D}" name="说明" dataDxfId="3"/>
-    <tableColumn id="14" xr3:uid="{43B77B9B-596D-4B8D-BAD8-C925F054EE0F}" name="位置状态" dataDxfId="2"/>
-    <tableColumn id="15" xr3:uid="{CDF395CC-09B1-D148-9811-7FBD24D5D85E}" name="Delivery date of position" dataDxfId="1"/>
-    <tableColumn id="16" xr3:uid="{0EF9D469-D9E9-B745-8229-8986EE2E2AF3}" name="Price" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{509C9033-BB95-4FBE-92A0-4CB515E0BEFD}" name="masterOrderImportSchema_en" displayName="masterOrderImportSchema_en" ref="A1:N2" insertRow="1" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+  <autoFilter ref="A1:N2" xr:uid="{509C9033-BB95-4FBE-92A0-4CB515E0BEFD}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{23FABA08-3273-4AB7-9597-4F5A70C4A802}" name="编号" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{333E4883-B023-4214-B42A-2955249499F1}" name="产品编号" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{C2C5E57D-6FF8-4AC2-9D39-0F486D2B0635}" name="数量" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{38BDA567-1F2F-4129-9971-CACDFC7230DF}" name="销售订单名称" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{712BB09D-F8B5-4BA0-8C6B-67E1428AD39D}" name="描述" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{D782C7E9-A47A-4544-AB5D-4D3E4A34E11C}" name="客户" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{8F187897-00A6-4184-9F3D-C9E9D6FFAE1A}" name="开始日期" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{2AEE7656-FC19-4A25-8B27-7F10864D6B66}" name="结束日期" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{0788B078-0DB2-449F-8885-09A8766A36F3}" name="截止日期" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{200873D5-3A9E-4F92-9648-637A95B6FF84}" name="接单日期" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{07928C99-1DDA-4CFC-AAC0-A58D0AC5D66A}" name="状态描述" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{AA8ABAE0-75A6-49F4-8A32-AA80FCA4EBD7}" name="工艺" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{404241C0-BE8D-4E09-8909-BD1C6A0AB30D}" name="说明" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{43B77B9B-596D-4B8D-BAD8-C925F054EE0F}" name="位置状态" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Styl tabeli 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motyw pakietu Office 2013–2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
-    <a:clrScheme name="Pakiet Office 2013–2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1894,7 +1823,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Pakiet Office 2013–2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2000,7 +1929,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Pakiet Office 2013–2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2142,7 +2071,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2153,16 +2082,16 @@
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="16.83203125" defaultRowHeight="16"/>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultColWidth="16.8984375" defaultRowHeight="15.6"/>
   <cols>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-    <col min="7" max="10" width="20.83203125" customWidth="1"/>
-    <col min="11" max="11" width="27.6640625" customWidth="1"/>
-    <col min="13" max="13" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20.8984375" customWidth="1"/>
+    <col min="7" max="10" width="20.8984375" customWidth="1"/>
+    <col min="11" max="11" width="27.59765625" customWidth="1"/>
+    <col min="13" max="13" width="20.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="18">
+    <row r="1" spans="1:14" ht="17.399999999999999">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2205,14 +2134,8 @@
       <c r="N1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:14">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2227,8 +2150,6 @@
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
